--- a/data/processed/positivacao/2026-06_positivacao_anonimizado.xlsx
+++ b/data/processed/positivacao/2026-06_positivacao_anonimizado.xlsx
@@ -551,7 +551,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Vendedor: 1 - ROBSON</t>
+          <t>Vendedor: 1 - VENDEDOR 01</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -26895,7 +26895,7 @@
     <row r="1022">
       <c r="A1022" t="inlineStr">
         <is>
-          <t>Vendedor: 3 - FERNANDA</t>
+          <t>Vendedor: 3 - VENDEDOR 03</t>
         </is>
       </c>
       <c r="B1022" t="inlineStr"/>
@@ -35621,7 +35621,7 @@
     <row r="1358">
       <c r="A1358" t="inlineStr">
         <is>
-          <t>Vendedor: 4 - DANIELA</t>
+          <t>Vendedor: 4 - VENDEDOR 04</t>
         </is>
       </c>
       <c r="B1358" t="inlineStr"/>
@@ -66801,7 +66801,7 @@
     <row r="2558">
       <c r="A2558" t="inlineStr">
         <is>
-          <t>Vendedor: 8 - RAFAEL</t>
+          <t>Vendedor: 8 - VENDEDOR 08</t>
         </is>
       </c>
       <c r="B2558" t="inlineStr"/>
@@ -68420,12 +68420,12 @@
       <c r="A2621" t="inlineStr"/>
       <c r="B2621" t="inlineStr">
         <is>
-          <t>Vendedor 1 - ROBSON: positivou 5 cliente(s), não positivou 86 cliente(s) - Total vendido: R$ 3.565,16
+          <t>Vendedor 1 - VENDEDOR 01: positivou 5 cliente(s), não positivou 86 cliente(s) - Total vendido: R$ 3.565,16
 Vendedor 18 - LOJA: positivou 287 cliente(s), não positivou 634 cliente(s) - Total vendido: R$ 92.232,69
-Vendedor 3 - FERNANDA: positivou 5 cliente(s), não positivou 330 cliente(s) - Total vendido: R$ 1.465,26
-Vendedor 4 - DANIELA: positivou 247 cliente(s), não positivou 503 cliente(s) - Total vendido: R$ 196.566,57
+Vendedor 3 - VENDEDOR 03: positivou 5 cliente(s), não positivou 330 cliente(s) - Total vendido: R$ 1.465,26
+Vendedor 4 - VENDEDOR 04: positivou 247 cliente(s), não positivou 503 cliente(s) - Total vendido: R$ 196.566,57
 Vendedor 5 - SITE: positivou 2 cliente(s), não positivou 446 cliente(s) - Total vendido: R$ 142,14
-Vendedor 8 - RAFAEL: positivou 0 cliente(s), não positivou 61 cliente(s) - Total vendido: R$ 0,00</t>
+Vendedor 8 - VENDEDOR 08: positivou 0 cliente(s), não positivou 61 cliente(s) - Total vendido: R$ 0,00</t>
         </is>
       </c>
       <c r="C2621" t="inlineStr"/>
